--- a/AAII_Financials/Quarterly/DLYT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLYT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>DLYT</t>
   </si>
@@ -1502,8 +1502,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>3100</v>
       </c>
       <c r="E17" s="3">
         <v>900</v>
@@ -1594,8 +1594,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
         <v>-500</v>
@@ -1720,8 +1720,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1812,8 +1812,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-2400</v>
       </c>
       <c r="E21" s="3">
         <v>-500</v>
@@ -1996,8 +1996,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>-3000</v>
       </c>
       <c r="E23" s="3">
         <v>-1000</v>
@@ -2272,8 +2272,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-3000</v>
       </c>
       <c r="E26" s="3">
         <v>-1000</v>
@@ -2364,8 +2364,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-3000</v>
       </c>
       <c r="E27" s="3">
         <v>-1000</v>
@@ -2824,8 +2824,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2916,8 +2916,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-3000</v>
       </c>
       <c r="E33" s="3">
         <v>-1000</v>
@@ -3100,8 +3100,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-3000</v>
       </c>
       <c r="E35" s="3">
         <v>-1000</v>
@@ -4370,7 +4370,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -4898,7 +4898,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="E59" s="3">
         <v>7500</v>
@@ -6684,8 +6684,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-3000</v>
       </c>
       <c r="E81" s="3">
         <v>-1000</v>
